--- a/packages/calculators/src/modules/test/4.4-sheep-manure/4.4-sheep-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.4-sheep-manure/4.4-sheep-manure.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/4.4-sheep-manure/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741FEBFC-9986-8445-BF7A-5DB929BB469A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61384379-87EE-D64C-9CDD-014421DBDC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.4.1.1" sheetId="13" r:id="rId1"/>
     <sheet name="Tables" sheetId="1" r:id="rId2"/>
     <sheet name="Backup" sheetId="12" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">Backup!$BW$6:$CE$30</definedName>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">Tables!$BW$6:$CE$30</definedName>
@@ -2921,6 +2919,31 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="19" xr16:uid="{7A92BB2C-3E9A-E544-BC0A-1E6BC2584CF5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="10">
@@ -4475,8 +4498,8 @@
         <v>150</v>
       </c>
       <c r="BZ7">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="8" spans="1:81" x14ac:dyDescent="0.2">
@@ -5143,7 +5166,7 @@
       </c>
       <c r="AY11" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ11">
         <f>$BZ$5</f>
@@ -5208,7 +5231,7 @@
       </c>
       <c r="BP11">
         <f>BM11 * BO11 * AY11 * 10^-3</f>
-        <v>3.0257057656854162E-3</v>
+        <v>3.0229551240802482E-3</v>
       </c>
       <c r="BQ11">
         <f>BK11 * AU11 * AV11</f>
@@ -5220,11 +5243,11 @@
       </c>
       <c r="BS11">
         <f>BK11 * AX11 * AY11 * 10^-3</f>
-        <v>4.802707564580027E-2</v>
+        <v>4.7983414667940455E-2</v>
       </c>
       <c r="BT11">
         <f>BQ11 * BR11 * AY11 * 10^-3</f>
-        <v>2.1131913284152117E-2</v>
+        <v>2.1112702453893798E-2</v>
       </c>
       <c r="CA11" s="13" t="s">
         <v>270</v>
@@ -9217,7 +9240,7 @@
       </c>
       <c r="AY41" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ41">
         <f>$BZ$5</f>
@@ -9282,7 +9305,7 @@
       </c>
       <c r="BP41">
         <f>BM41 * BO41 * AY41 * 10^-3</f>
-        <v>4.8747481780487267E-3</v>
+        <v>4.8703165887959551E-3</v>
       </c>
       <c r="BQ41">
         <f>BK41 * AU41 * AV41</f>
@@ -9294,7 +9317,7 @@
       </c>
       <c r="BS41">
         <f>BK41 * AX41 * AY41 * 10^-3</f>
-        <v>1.6009025215266755E-2</v>
+        <v>1.599447155598015E-2</v>
       </c>
       <c r="BT41">
         <f>BQ41 * BR41 * AY41 * 10^-3</f>
@@ -13203,7 +13226,7 @@
       </c>
       <c r="AY71" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ71">
         <f>$BZ$5</f>
@@ -13268,7 +13291,7 @@
       </c>
       <c r="BP71">
         <f>BM71 * BO71 * AY71 * 10^-3</f>
-        <v>3.2550768654959479E-3</v>
+        <v>3.2521177047091336E-3</v>
       </c>
       <c r="BQ71">
         <f>BK71 * AU71 * AV71</f>
@@ -13280,11 +13303,11 @@
       </c>
       <c r="BS71">
         <f>BK71 * AX71 * AY71 * 10^-3</f>
-        <v>1.1625274519628385E-2</v>
+        <v>1.1614706088246907E-2</v>
       </c>
       <c r="BT71">
         <f>BQ71 * BR71 * AY71 * 10^-3</f>
-        <v>5.1151207886364885E-3</v>
+        <v>5.110470678828638E-3</v>
       </c>
     </row>
     <row r="72" spans="1:72" x14ac:dyDescent="0.2">
@@ -17081,7 +17104,7 @@
       </c>
       <c r="AY101" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ101">
         <f>$BZ$5</f>
@@ -17146,7 +17169,7 @@
       </c>
       <c r="BP101">
         <f>BM101 * BO101 * AY101 * 10^-3</f>
-        <v>1.024672781058053E-2</v>
+        <v>1.0237412603480003E-2</v>
       </c>
       <c r="BQ101">
         <f>BK101 * AU101 * AV101</f>
@@ -17158,7 +17181,7 @@
       </c>
       <c r="BS101">
         <f>BK101 * AX101 * AY101 * 10^-3</f>
-        <v>3.659545646635904E-2</v>
+        <v>3.6562187869571439E-2</v>
       </c>
       <c r="BT101">
         <f>BQ101 * BR101 * AY101 * 10^-3</f>
@@ -20959,7 +20982,7 @@
       </c>
       <c r="AY131" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ131">
         <f>$BZ$5</f>
@@ -21024,7 +21047,7 @@
       </c>
       <c r="BP131">
         <f>BM131 * BO131 * AY131 * 10^-3</f>
-        <v>7.9881142092920517E-3</v>
+        <v>7.9808522872836032E-3</v>
       </c>
       <c r="BQ131">
         <f>BK131 * AU131 * AV131</f>
@@ -21036,11 +21059,11 @@
       </c>
       <c r="BS131">
         <f>BK131 * AX131 * AY131 * 10^-3</f>
-        <v>1.2894453929446411E-2</v>
+        <v>1.2882731698601461E-2</v>
       </c>
       <c r="BT131">
         <f>BQ131 * BR131 * AY131 * 10^-3</f>
-        <v>1.702067918686926E-2</v>
+        <v>1.7005205842153925E-2</v>
       </c>
     </row>
     <row r="132" spans="1:72" x14ac:dyDescent="0.2">
@@ -24837,7 +24860,7 @@
       </c>
       <c r="AY161" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ161">
         <f>$BZ$5</f>
@@ -24902,7 +24925,7 @@
       </c>
       <c r="BP161">
         <f>BM161 * BO161 * AY161 * 10^-3</f>
-        <v>1.7553056031409751E-3</v>
+        <v>1.7537098707744833E-3</v>
       </c>
       <c r="BQ161">
         <f>BK161 * AU161 * AV161</f>
@@ -24914,7 +24937,7 @@
       </c>
       <c r="BS161">
         <f>BK161 * AX161 * AY161 * 10^-3</f>
-        <v>9.2873312335501335E-3</v>
+        <v>9.2788882051559971E-3</v>
       </c>
       <c r="BT161">
         <f>BQ161 * BR161 * AY161 * 10^-3</f>
@@ -28715,7 +28738,7 @@
       </c>
       <c r="AY191" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ191">
         <f>$BZ$5</f>
@@ -28780,7 +28803,7 @@
       </c>
       <c r="BP191">
         <f>BM191 * BO191 * AY191 * 10^-3</f>
-        <v>2.3429556134654931E-3</v>
+        <v>2.3408256538168886E-3</v>
       </c>
       <c r="BQ191">
         <f>BK191 * AU191 * AV191</f>
@@ -28792,11 +28815,11 @@
       </c>
       <c r="BS191">
         <f>BK191 * AX191 * AY191 * 10^-3</f>
-        <v>3.7189771642309424E-2</v>
+        <v>3.7155962758998233E-2</v>
       </c>
       <c r="BT191">
         <f>BQ191 * BR191 * AY191 * 10^-3</f>
-        <v>1.6363499522616145E-2</v>
+        <v>1.6348623613959223E-2</v>
       </c>
     </row>
     <row r="192" spans="1:72" x14ac:dyDescent="0.2">
@@ -32599,7 +32622,7 @@
       </c>
       <c r="AY231" s="28">
         <f>$BZ$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AZ231">
         <f>$BZ$5</f>
@@ -32664,7 +32687,7 @@
       </c>
       <c r="BP231">
         <f>BM231 * BO231 * AY231 * 10^-3</f>
-        <v>2.4080077314403499E-5</v>
+        <v>2.405818633502677E-5</v>
       </c>
       <c r="BQ231">
         <f>BJ231 * AP231 * AV231</f>
@@ -32676,11 +32699,11 @@
       </c>
       <c r="BS231">
         <f>BK231 * AX231 * AY231 * 10^-3</f>
-        <v>9.4102272527152708E-3</v>
+        <v>9.4016725006673494E-3</v>
       </c>
       <c r="BT231">
         <f>BQ231 * BR231 * AY231 * 10^-3</f>
-        <v>9.9895338635597103E-9</v>
+        <v>9.9804524691382944E-9</v>
       </c>
     </row>
     <row r="232" spans="1:72" x14ac:dyDescent="0.2">
@@ -41216,8 +41239,8 @@
         <v>150</v>
       </c>
       <c r="BS7">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="BW7" t="s">
         <v>163</v>
@@ -42039,7 +42062,7 @@
       </c>
       <c r="AN11">
         <f>$BS$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO11">
         <f>$BV$1</f>
@@ -42127,15 +42150,15 @@
       </c>
       <c r="BJ11">
         <f>BF11 * AM11 * AN11 * 10^-3</f>
-        <v>3.4316918378220064E-3</v>
+        <v>3.428572117969441E-3</v>
       </c>
       <c r="BK11">
         <f>BH11 * AB11 * AN11 * 10^-3</f>
-        <v>7.0864436451024428E-4</v>
+        <v>7.0800014236068951E-4</v>
       </c>
       <c r="BL11">
         <f>BI11 * Z11 * AN11 * 10^-3</f>
-        <v>1.5099444086416828E-3</v>
+        <v>1.5085717319065542E-3</v>
       </c>
       <c r="BT11" s="13" t="s">
         <v>194</v>
@@ -42316,7 +42339,7 @@
       </c>
       <c r="AN12">
         <f t="shared" ref="AN12:AN34" si="24">$BS$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO12">
         <f t="shared" ref="AO12:AO34" si="25">$BV$1</f>
@@ -42561,7 +42584,7 @@
       </c>
       <c r="AN13">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO13">
         <f t="shared" si="25"/>
@@ -42803,7 +42826,7 @@
       </c>
       <c r="AN14">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO14">
         <f t="shared" si="25"/>
@@ -43045,7 +43068,7 @@
       </c>
       <c r="AN15">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO15">
         <f t="shared" si="25"/>
@@ -43287,7 +43310,7 @@
       </c>
       <c r="AN16">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO16">
         <f t="shared" si="25"/>
@@ -43532,7 +43555,7 @@
       </c>
       <c r="AN17">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO17">
         <f t="shared" si="25"/>
@@ -43768,7 +43791,7 @@
       </c>
       <c r="AN18">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO18">
         <f t="shared" si="25"/>
@@ -44013,7 +44036,7 @@
       </c>
       <c r="AN19">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO19">
         <f t="shared" si="25"/>
@@ -44255,7 +44278,7 @@
       </c>
       <c r="AN20">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO20">
         <f t="shared" si="25"/>
@@ -44500,7 +44523,7 @@
       </c>
       <c r="AN21">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO21">
         <f t="shared" si="25"/>
@@ -44736,7 +44759,7 @@
       </c>
       <c r="AN22">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO22">
         <f t="shared" si="25"/>
@@ -44972,7 +44995,7 @@
       </c>
       <c r="AN23">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO23">
         <f t="shared" si="25"/>
@@ -45208,7 +45231,7 @@
       </c>
       <c r="AN24">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO24">
         <f t="shared" si="25"/>
@@ -45447,7 +45470,7 @@
       </c>
       <c r="AN25">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO25">
         <f t="shared" si="25"/>
@@ -45686,7 +45709,7 @@
       </c>
       <c r="AN26">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO26">
         <f t="shared" si="25"/>
@@ -45931,7 +45954,7 @@
       </c>
       <c r="AN27">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO27">
         <f t="shared" si="25"/>
@@ -46176,7 +46199,7 @@
       </c>
       <c r="AN28">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO28">
         <f t="shared" si="25"/>
@@ -46424,7 +46447,7 @@
       </c>
       <c r="AN29">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO29">
         <f t="shared" si="25"/>
@@ -46669,7 +46692,7 @@
       </c>
       <c r="AN30">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO30">
         <f t="shared" si="25"/>
@@ -46914,7 +46937,7 @@
       </c>
       <c r="AN31">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO31">
         <f t="shared" si="25"/>
@@ -47132,7 +47155,7 @@
       </c>
       <c r="AN32">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO32">
         <f t="shared" si="25"/>
@@ -47329,7 +47352,7 @@
       </c>
       <c r="AN33">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO33">
         <f t="shared" si="25"/>
@@ -47517,7 +47540,7 @@
       </c>
       <c r="AN34">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO34">
         <f t="shared" si="25"/>
@@ -55768,8 +55791,8 @@
         <v>150</v>
       </c>
       <c r="BS7">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="BW7" t="s">
         <v>163</v>
@@ -56591,7 +56614,7 @@
       </c>
       <c r="AN11">
         <f>$BS$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO11">
         <f>$BV$1</f>
@@ -56679,15 +56702,15 @@
       </c>
       <c r="BJ11">
         <f>BF11 * AM11 * AN11 * 10^-3</f>
-        <v>3.4316918378220064E-3</v>
+        <v>3.428572117969441E-3</v>
       </c>
       <c r="BK11">
         <f>BH11 * AB11 * AN11 * 10^-3</f>
-        <v>7.0864436451024428E-4</v>
+        <v>7.0800014236068951E-4</v>
       </c>
       <c r="BL11">
         <f>BI11 * Z11 * AN11 * 10^-3</f>
-        <v>1.5099444086416828E-3</v>
+        <v>1.5085717319065542E-3</v>
       </c>
       <c r="BT11" s="13" t="s">
         <v>194</v>
@@ -56868,7 +56891,7 @@
       </c>
       <c r="AN12">
         <f t="shared" ref="AN12:AN34" si="24">$BS$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO12">
         <f t="shared" ref="AO12:AO34" si="25">$BV$1</f>
@@ -57113,7 +57136,7 @@
       </c>
       <c r="AN13">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO13">
         <f t="shared" si="25"/>
@@ -57355,7 +57378,7 @@
       </c>
       <c r="AN14">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO14">
         <f t="shared" si="25"/>
@@ -57597,7 +57620,7 @@
       </c>
       <c r="AN15">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO15">
         <f t="shared" si="25"/>
@@ -57839,7 +57862,7 @@
       </c>
       <c r="AN16">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO16">
         <f t="shared" si="25"/>
@@ -58084,7 +58107,7 @@
       </c>
       <c r="AN17">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO17">
         <f t="shared" si="25"/>
@@ -58320,7 +58343,7 @@
       </c>
       <c r="AN18">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO18">
         <f t="shared" si="25"/>
@@ -58565,7 +58588,7 @@
       </c>
       <c r="AN19">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO19">
         <f t="shared" si="25"/>
@@ -58807,7 +58830,7 @@
       </c>
       <c r="AN20">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO20">
         <f t="shared" si="25"/>
@@ -59052,7 +59075,7 @@
       </c>
       <c r="AN21">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO21">
         <f t="shared" si="25"/>
@@ -59288,7 +59311,7 @@
       </c>
       <c r="AN22">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO22">
         <f t="shared" si="25"/>
@@ -59524,7 +59547,7 @@
       </c>
       <c r="AN23">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO23">
         <f t="shared" si="25"/>
@@ -59760,7 +59783,7 @@
       </c>
       <c r="AN24">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO24">
         <f t="shared" si="25"/>
@@ -59999,7 +60022,7 @@
       </c>
       <c r="AN25">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO25">
         <f t="shared" si="25"/>
@@ -60238,7 +60261,7 @@
       </c>
       <c r="AN26">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO26">
         <f t="shared" si="25"/>
@@ -60483,7 +60506,7 @@
       </c>
       <c r="AN27">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO27">
         <f t="shared" si="25"/>
@@ -60728,7 +60751,7 @@
       </c>
       <c r="AN28">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO28">
         <f t="shared" si="25"/>
@@ -60976,7 +60999,7 @@
       </c>
       <c r="AN29">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO29">
         <f t="shared" si="25"/>
@@ -61221,7 +61244,7 @@
       </c>
       <c r="AN30">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO30">
         <f t="shared" si="25"/>
@@ -61466,7 +61489,7 @@
       </c>
       <c r="AN31">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO31">
         <f t="shared" si="25"/>
@@ -61684,7 +61707,7 @@
       </c>
       <c r="AN32">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO32">
         <f t="shared" si="25"/>
@@ -61881,7 +61904,7 @@
       </c>
       <c r="AN33">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO33">
         <f t="shared" si="25"/>
@@ -62069,7 +62092,7 @@
       </c>
       <c r="AN34">
         <f t="shared" si="24"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AO34">
         <f t="shared" si="25"/>
